--- a/Data/HRM/HRM_Quizzes.xlsx
+++ b/Data/HRM/HRM_Quizzes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba\Data\Semester 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba_quiz\Data\HRM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBCC6336-8934-422F-A860-757A19D123D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EF12E8-1A21-410D-B081-2978C2E5F55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="11" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="13" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <definedName name="ExternalData_1" localSheetId="0" hidden="1">'Week 1'!$A$1:$F$21</definedName>
     <definedName name="ExternalData_10" localSheetId="9" hidden="1">'Week 10'!$A$1:$F$21</definedName>
     <definedName name="ExternalData_11" localSheetId="10" hidden="1">'Week 11'!$A$1:$F$21</definedName>
-    <definedName name="ExternalData_12" localSheetId="11" hidden="1">'Week 12'!$A$1:$L$9</definedName>
+    <definedName name="ExternalData_12" localSheetId="11" hidden="1">'Week 12'!$A$1:$F$9</definedName>
     <definedName name="ExternalData_2" localSheetId="1" hidden="1">'Week 2'!$A$1:$F$21</definedName>
     <definedName name="ExternalData_3" localSheetId="2" hidden="1">'Week 3'!$A$1:$F$21</definedName>
     <definedName name="ExternalData_4" localSheetId="3" hidden="1">'Week 4'!$A$1:$F$21</definedName>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="1108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="1103">
   <si>
     <t xml:space="preserve">Question 1 </t>
   </si>
@@ -3128,9 +3128,6 @@
     <t>Reduce insurance premiums only</t>
   </si>
   <si>
-    <t xml:space="preserve">IncorrectQuestion 5 </t>
-  </si>
-  <si>
     <t>An employee develops severe wrist pain after years of repetitive tool usage. Which category explains this risk?</t>
   </si>
   <si>
@@ -3413,22 +3410,10 @@
     <t>1961</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>Answer</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
@@ -3470,10 +3455,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -3522,14 +3504,15 @@
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_1" connectionId="1" xr16:uid="{0A9A6E0D-95C3-481A-8C5C-2905A3202D10}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3537,14 +3520,15 @@
 
 <file path=xl/queryTables/queryTable10.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_10" connectionId="2" xr16:uid="{1A8928FF-DA20-4D39-A594-8C6D3F7BB8E0}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3552,35 +3536,15 @@
 
 <file path=xl/queryTables/queryTable11.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_11" connectionId="3" xr16:uid="{F4C4D9DE-A9B0-4BA8-979F-0C00EA3C52B6}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
-    </queryTableFields>
-  </queryTableRefresh>
-</queryTable>
-</file>
-
-<file path=xl/queryTables/queryTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_12" connectionId="4" xr16:uid="{2200A6D3-57FC-490B-958A-49FC9852E528}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="13">
-    <queryTableFields count="12">
-      <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
-      <queryTableField id="2" name="Question" tableColumnId="2"/>
-      <queryTableField id="3" name="Option_A" tableColumnId="3"/>
-      <queryTableField id="4" name="Option_B" tableColumnId="4"/>
-      <queryTableField id="5" name="Option_C" tableColumnId="5"/>
-      <queryTableField id="6" name="Option_D" tableColumnId="6"/>
-      <queryTableField id="7" name="6" tableColumnId="7"/>
-      <queryTableField id="8" name="7" tableColumnId="8"/>
-      <queryTableField id="9" name="8" tableColumnId="9"/>
-      <queryTableField id="10" name="9" tableColumnId="10"/>
-      <queryTableField id="11" name="10" tableColumnId="11"/>
-      <queryTableField id="12" name="11" tableColumnId="12"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3588,14 +3552,15 @@
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_2" connectionId="5" xr16:uid="{EF4B5BEB-CA3E-4CBC-852D-E2C9FF1C8C71}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3603,14 +3568,15 @@
 
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_3" connectionId="6" xr16:uid="{10274897-332A-4283-B035-5C55E61912B1}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3618,14 +3584,15 @@
 
 <file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_4" connectionId="7" xr16:uid="{170E7C85-FED2-409D-9EF4-339BC204B39D}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3633,14 +3600,15 @@
 
 <file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_5" connectionId="8" xr16:uid="{31EF0943-1A34-4C67-8314-0630065AA3B9}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3648,14 +3616,15 @@
 
 <file path=xl/queryTables/queryTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_6" connectionId="9" xr16:uid="{BBC09D6C-6E2B-41BB-99DE-4DF0609FCD72}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3663,14 +3632,15 @@
 
 <file path=xl/queryTables/queryTable7.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_7" connectionId="10" xr16:uid="{E5B80A15-A67F-4593-8726-D06C25402FBF}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3678,14 +3648,15 @@
 
 <file path=xl/queryTables/queryTable8.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_8" connectionId="11" xr16:uid="{D8ADDF2A-143C-4E19-AB35-028B31A09E40}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
@@ -3693,200 +3664,207 @@
 
 <file path=xl/queryTables/queryTable9.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="ExternalData_9" connectionId="12" xr16:uid="{EA4AD27C-B4F3-4761-9B21-E618310293A8}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0">
-  <queryTableRefresh nextId="7">
-    <queryTableFields count="6">
+  <queryTableRefresh nextId="8" unboundColumnsRight="1">
+    <queryTableFields count="7">
       <queryTableField id="1" name="QuestionID" tableColumnId="1"/>
       <queryTableField id="2" name="Question" tableColumnId="2"/>
       <queryTableField id="3" name="Option_A" tableColumnId="3"/>
       <queryTableField id="4" name="Option_B" tableColumnId="4"/>
       <queryTableField id="5" name="Option_C" tableColumnId="5"/>
       <queryTableField id="6" name="Option_D" tableColumnId="6"/>
+      <queryTableField id="7" dataBound="0" tableColumnId="7"/>
     </queryTableFields>
   </queryTableRefresh>
 </queryTable>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{538EEDBA-9B73-431E-87C2-EC7AB5CB1DE7}" name="Invoked_Function" displayName="Invoked_Function" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{538EEDBA-9B73-431E-87C2-EC7AB5CB1DE7}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F599255B-77EF-421C-BC43-F575F0D2D389}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{538EEDBA-9B73-431E-87C2-EC7AB5CB1DE7}" name="Invoked_Function" displayName="Invoked_Function" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{538EEDBA-9B73-431E-87C2-EC7AB5CB1DE7}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{F599255B-77EF-421C-BC43-F575F0D2D389}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{F9037DE6-3F6F-4929-8D3D-6CC3BA23249E}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{CC2ED0DA-041A-4783-90CB-838D55ADB421}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{CE685B90-37D4-407A-9793-AEBBE45D2408}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{01F99526-F26E-44C9-A443-8FC84022C8CC}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{8AB7097E-8AD5-40D1-A3D7-2494DB2D470F}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{890E551F-5CF1-446C-A08F-55D765A0E05D}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{A458C2F0-5314-46D4-86CC-16A0BB56D714}" name="Invoked_Function__10" displayName="Invoked_Function__10" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{A458C2F0-5314-46D4-86CC-16A0BB56D714}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{A3B2750A-27F3-4A7E-BEB8-FDAC5FD687EF}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{A458C2F0-5314-46D4-86CC-16A0BB56D714}" name="Invoked_Function__10" displayName="Invoked_Function__10" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{A458C2F0-5314-46D4-86CC-16A0BB56D714}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{A3B2750A-27F3-4A7E-BEB8-FDAC5FD687EF}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{3E1DAE0D-A68A-4B90-8C95-493D26B5F28C}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{A8A1A4F9-D04D-44D8-9948-311EE9B9CA0F}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{7C39C9C2-AD88-444F-927B-6D9263104D72}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{B6938A28-D862-42D4-9564-3ACEC69FB83A}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{4E77E074-B577-493A-AD6D-21A28CBEC011}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{A85A07EE-52B6-4F89-938A-6CEBCC9DBA08}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{64D72B6C-7F08-4A24-8806-49258EF03D45}" name="Invoked_Function__11" displayName="Invoked_Function__11" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{64D72B6C-7F08-4A24-8806-49258EF03D45}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{EA94E98E-8769-46CC-B5E8-88C1D3494BFC}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{64D72B6C-7F08-4A24-8806-49258EF03D45}" name="Invoked_Function__11" displayName="Invoked_Function__11" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{64D72B6C-7F08-4A24-8806-49258EF03D45}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{EA94E98E-8769-46CC-B5E8-88C1D3494BFC}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{70125CEA-CAAF-4904-92D6-9416D65BCFEB}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{0BAAD36D-EDCD-458C-9D28-7DF4E35A5CA2}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{54AC8831-B033-452D-AAEB-F1F1E4119E3F}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{FD344ADC-CC0E-4D72-A802-2A5982BEDFC7}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{C4D98D17-6F0E-42D7-BAD4-D07321A5B0C7}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{28E38ED5-DC68-4586-AB06-597F37DA23A2}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{4BB54CA4-BF70-42AB-885A-041CA19CD3D1}" name="Invoked_Function__12" displayName="Invoked_Function__12" ref="A1:L21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:L21" xr:uid="{4BB54CA4-BF70-42AB-885A-041CA19CD3D1}"/>
-  <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{826240BD-ADAD-4D78-937A-A334F564F1F4}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{988C5929-B410-4C4A-B5FA-123AEA69AFD4}" uniqueName="2" name="Question" queryTableFieldId="2"/>
-    <tableColumn id="3" xr3:uid="{3E115820-0167-421E-9752-FDD6E2D0CEC2}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
-    <tableColumn id="4" xr3:uid="{9D0DDD4F-C276-4B9D-88D6-4C50A09D1585}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
-    <tableColumn id="5" xr3:uid="{50572BE7-2E12-4567-A3E7-2C6FA33FA539}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
-    <tableColumn id="6" xr3:uid="{B0C67E5E-8776-4DC3-ADEB-C391E4C755CB}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
-    <tableColumn id="7" xr3:uid="{19CEE252-A5AE-43D9-B468-71077871B033}" uniqueName="7" name="6" queryTableFieldId="7"/>
-    <tableColumn id="8" xr3:uid="{F8F55DF3-F222-44DA-A3AA-8317F5390DD1}" uniqueName="8" name="7" queryTableFieldId="8"/>
-    <tableColumn id="9" xr3:uid="{26876D39-0C0C-482C-BE6F-88A5344D65F8}" uniqueName="9" name="8" queryTableFieldId="9"/>
-    <tableColumn id="10" xr3:uid="{B052D0CF-1DB5-4643-8D61-8F03E6676C24}" uniqueName="10" name="9" queryTableFieldId="10"/>
-    <tableColumn id="11" xr3:uid="{4DE5E252-09FA-406D-9782-FE111E4077F3}" uniqueName="11" name="10" queryTableFieldId="11"/>
-    <tableColumn id="12" xr3:uid="{487066EB-D49F-49A8-B592-1BA39CA2386B}" uniqueName="12" name="11" queryTableFieldId="12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F3E5A435-8419-46F2-9627-AC87F29F3CFD}" name="Table2" displayName="Table2" ref="A1:G21" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{F3E5A435-8419-46F2-9627-AC87F29F3CFD}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{DFA63737-D547-43EA-9169-E388BFBAEB6C}" name="QuestionID"/>
+    <tableColumn id="2" xr3:uid="{3E11C679-F835-4CA7-878A-3C2B34E4DE8A}" name="Question"/>
+    <tableColumn id="3" xr3:uid="{97A7B121-749D-4A31-80AE-E1E852818252}" name="Option_A"/>
+    <tableColumn id="4" xr3:uid="{6AC23F5C-0205-4066-997D-4808B01F7728}" name="Option_B"/>
+    <tableColumn id="5" xr3:uid="{51ACCE04-0B32-4DE3-9C73-FF9369ACA97B}" name="Option_C"/>
+    <tableColumn id="6" xr3:uid="{5C6BF92F-997D-4A06-BD6C-9741CF77E0E0}" name="Option_D"/>
+    <tableColumn id="7" xr3:uid="{6356671D-28C3-451D-ABC8-8820774C0CF2}" name="Answer"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{D476988A-A03F-43E3-953D-057325572397}" name="Invoked_Function__2" displayName="Invoked_Function__2" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{D476988A-A03F-43E3-953D-057325572397}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{605EF333-5722-493C-82E0-12B760CE7067}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{D476988A-A03F-43E3-953D-057325572397}" name="Invoked_Function__2" displayName="Invoked_Function__2" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{D476988A-A03F-43E3-953D-057325572397}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{605EF333-5722-493C-82E0-12B760CE7067}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{042D1B72-808B-4960-85C5-536138CEE3DE}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{5D059C41-8EED-4120-B4F8-67E6CEC2B24C}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{20CE8CD6-7C5E-4EA2-A135-BAA225C79362}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{0A74B06C-2759-4DBE-B3C6-691EF33AA5D0}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{8AF44403-02C2-4A96-BC29-1C9C1B84FC52}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{94B3FC17-FA9D-45F0-9C01-525379F55B32}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{2493896C-A371-4C58-AE23-34F325B82283}" name="Invoked_Function__3" displayName="Invoked_Function__3" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{2493896C-A371-4C58-AE23-34F325B82283}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{C621114B-B9CA-462D-BFAF-247A7FD9C7E6}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{2493896C-A371-4C58-AE23-34F325B82283}" name="Invoked_Function__3" displayName="Invoked_Function__3" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{2493896C-A371-4C58-AE23-34F325B82283}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{C621114B-B9CA-462D-BFAF-247A7FD9C7E6}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{5B729A9B-6D93-48C6-A805-530D7AFB6651}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{1AABFCC3-CDF8-4CCE-88C8-5EE20FBBE7D8}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{86BE7E48-3954-4F04-852D-6AD757F15566}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{3CDEFB4D-8E6E-4AFD-B1EE-BBB83EC7B58E}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{C27EAD96-8583-4C88-ADF7-695FA3412AB6}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{CE0B4F27-679A-4DF1-A0F6-884D7156D2D6}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{8CF9526B-0C69-43D2-8248-B78E06868964}" name="Invoked_Function__4" displayName="Invoked_Function__4" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{8CF9526B-0C69-43D2-8248-B78E06868964}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8E99948E-F064-4567-A246-73D9CA11E083}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{8CF9526B-0C69-43D2-8248-B78E06868964}" name="Invoked_Function__4" displayName="Invoked_Function__4" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{8CF9526B-0C69-43D2-8248-B78E06868964}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{8E99948E-F064-4567-A246-73D9CA11E083}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{9B57E41B-6B27-4270-AF9D-6800752C267E}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{F6FCAF3B-8841-4362-AB13-A1B34B118553}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{F401941F-B30C-47C9-A80E-8A412A8BD088}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{FC847DB1-AF5E-43DD-B9F6-3BE8242F8808}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{D4077742-0C5B-4E72-B4CB-E1ED8D00D1AD}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{8E48F979-CC1B-4A49-93E1-BD088100ACE9}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{630DF0C7-A642-464E-B088-DD948311C487}" name="Invoked_Function__5" displayName="Invoked_Function__5" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{630DF0C7-A642-464E-B088-DD948311C487}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{49F8398D-86A9-4EAE-8952-759BCE4D98AF}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{630DF0C7-A642-464E-B088-DD948311C487}" name="Invoked_Function__5" displayName="Invoked_Function__5" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{630DF0C7-A642-464E-B088-DD948311C487}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{49F8398D-86A9-4EAE-8952-759BCE4D98AF}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{B31E6E79-19D8-41A9-B943-CCDC9E1047EA}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{5046AFE6-EDFF-4D24-9AB4-8C345BADEC3D}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{82A3762B-C370-412F-9FA6-86FFBC9DD42D}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{923A4107-FE04-4CB5-B5CA-A1825879BDBD}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{F718C20A-7AC3-4D38-98E0-5DAE5033D040}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{2D91E89C-3374-4CC1-95E2-8628F306FDB7}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{F878B18C-1BF7-4F22-B23B-22B0371F00E7}" name="Invoked_Function__6" displayName="Invoked_Function__6" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{F878B18C-1BF7-4F22-B23B-22B0371F00E7}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{F878B18C-1BF7-4F22-B23B-22B0371F00E7}" name="Invoked_Function__6" displayName="Invoked_Function__6" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{F878B18C-1BF7-4F22-B23B-22B0371F00E7}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{C25841B3-DDDF-42A6-BBEE-14A7961B8950}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{BA4C1515-CA9D-4DFF-B08D-714CA9B378AA}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{AEE8A806-C2B4-4001-AFD8-5ACC84846AA0}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{8BC6E0BA-5FF4-460B-B699-EEC07FEEE59A}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{16763CE1-4EF7-4693-BA2D-FFA89BBF69B0}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{D96107E7-D9DD-457D-A333-220EA5C0152E}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{33A5140B-F600-46B2-B060-53E040575D43}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{8C2F89B4-E03C-442F-B7E8-6AA63C7285D9}" name="Invoked_Function__7" displayName="Invoked_Function__7" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{8C2F89B4-E03C-442F-B7E8-6AA63C7285D9}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{2D8418AB-FCD1-4B6F-AF10-F9094E63B6DA}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{8C2F89B4-E03C-442F-B7E8-6AA63C7285D9}" name="Invoked_Function__7" displayName="Invoked_Function__7" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{8C2F89B4-E03C-442F-B7E8-6AA63C7285D9}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{2D8418AB-FCD1-4B6F-AF10-F9094E63B6DA}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{5FE58BE0-7E4D-461A-A1C1-AE690F3724ED}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{30DD1391-CD8B-4CDF-8501-69325B214960}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{0182432B-D43D-45E0-B683-16CEF8E9E6DC}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{A742733B-ECD7-49D3-9C86-B4EED34D3FEB}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{1FECFB8D-E18E-479B-982C-43684A5CD951}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{13533E74-0E8E-4539-AD13-D4F37DEBE01B}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{486C2A8A-BAC1-4CF8-9F56-547EAA3A4E83}" name="Invoked_Function__8" displayName="Invoked_Function__8" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{486C2A8A-BAC1-4CF8-9F56-547EAA3A4E83}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{64A53E32-7AA1-4F11-BD01-CDA508EFC0CA}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{486C2A8A-BAC1-4CF8-9F56-547EAA3A4E83}" name="Invoked_Function__8" displayName="Invoked_Function__8" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{486C2A8A-BAC1-4CF8-9F56-547EAA3A4E83}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{64A53E32-7AA1-4F11-BD01-CDA508EFC0CA}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{3DBC2F52-F019-457B-93B7-EAF3F474C325}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{127D2DFA-24B3-4067-B62F-339E00C85C62}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{A77ED5BD-F15F-4558-AF9C-BF5BABB0266B}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{DE7CE2BA-B5C6-4A52-9829-8433AAFDEDA1}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{A7CDA2FE-D824-460B-B347-2DF25548C071}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{D315A7BC-0131-44B4-BAA8-E0C50D196283}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{3ED021C4-F6DF-4C65-96B4-CA439D902DAF}" name="Invoked_Function__9" displayName="Invoked_Function__9" ref="A1:F21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:F21" xr:uid="{3ED021C4-F6DF-4C65-96B4-CA439D902DAF}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{451FD237-E5B3-4EF2-BC40-19A77FC26C18}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{3ED021C4-F6DF-4C65-96B4-CA439D902DAF}" name="Invoked_Function__9" displayName="Invoked_Function__9" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:G21" xr:uid="{3ED021C4-F6DF-4C65-96B4-CA439D902DAF}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{451FD237-E5B3-4EF2-BC40-19A77FC26C18}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{248CB54E-57CF-448A-9A91-AC65DB84B0E7}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{EE822D66-B546-4BB8-981B-E65761A57BD4}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{76E01E24-686A-47BC-94FC-F85B09563D65}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{AF04A068-05E2-46B4-9532-1AD3E231EE4A}" uniqueName="5" name="Option_C" queryTableFieldId="5"/>
     <tableColumn id="6" xr3:uid="{F1F1E446-F021-4C17-9F56-7EF5812A62F9}" uniqueName="6" name="Option_D" queryTableFieldId="6"/>
+    <tableColumn id="7" xr3:uid="{31800221-6C48-4002-BAB0-718A310DB15D}" uniqueName="7" name="Answer" queryTableFieldId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4210,7 +4188,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{218E20C1-5F06-4584-83C2-45A7B82A2714}">
   <sheetPr codeName="Sheet24"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -4221,27 +4199,30 @@
     <col min="6" max="6" width="58" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B1" t="s">
         <v>1088</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1089</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1090</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1091</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1092</v>
       </c>
-      <c r="F1" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4260,8 +4241,11 @@
       <c r="F2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4280,8 +4264,11 @@
       <c r="F3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -4300,8 +4287,11 @@
       <c r="F4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4320,8 +4310,11 @@
       <c r="F5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -4340,8 +4333,11 @@
       <c r="F6" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -4360,8 +4356,11 @@
       <c r="F7" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -4380,8 +4379,11 @@
       <c r="F8" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -4400,8 +4402,11 @@
       <c r="F9" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -4420,8 +4425,11 @@
       <c r="F10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -4440,8 +4448,11 @@
       <c r="F11" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -4460,8 +4471,11 @@
       <c r="F12" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -4480,8 +4494,11 @@
       <c r="F13" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -4500,8 +4517,11 @@
       <c r="F14" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -4520,8 +4540,11 @@
       <c r="F15" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>80</v>
       </c>
@@ -4540,8 +4563,11 @@
       <c r="F16" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -4560,8 +4586,11 @@
       <c r="F17" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -4580,8 +4609,11 @@
       <c r="F18" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -4600,8 +4632,11 @@
       <c r="F19" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -4620,8 +4655,11 @@
       <c r="F20" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -4639,6 +4677,9 @@
       </c>
       <c r="F21" t="s">
         <v>113</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1102</v>
       </c>
     </row>
   </sheetData>
@@ -4652,7 +4693,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D9B8FCA-3694-4A16-A9C2-47CDEF9CF698}">
   <sheetPr codeName="Sheet15"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -4663,27 +4704,30 @@
     <col min="6" max="6" width="31.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B1" t="s">
         <v>1088</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1089</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1090</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1091</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1092</v>
       </c>
-      <c r="F1" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4702,8 +4746,11 @@
       <c r="F2" t="s">
         <v>796</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4722,8 +4769,11 @@
       <c r="F3" t="s">
         <v>801</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -4742,8 +4792,11 @@
       <c r="F4" t="s">
         <v>806</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -4762,8 +4815,11 @@
       <c r="F5" t="s">
         <v>811</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -4782,8 +4838,11 @@
       <c r="F6" t="s">
         <v>816</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -4802,8 +4861,11 @@
       <c r="F7" t="s">
         <v>821</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -4822,8 +4884,11 @@
       <c r="F8" t="s">
         <v>826</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -4842,8 +4907,11 @@
       <c r="F9" t="s">
         <v>831</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -4862,8 +4930,11 @@
       <c r="F10" t="s">
         <v>835</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -4882,8 +4953,11 @@
       <c r="F11" t="s">
         <v>840</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -4902,8 +4976,11 @@
       <c r="F12" t="s">
         <v>845</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -4922,8 +4999,11 @@
       <c r="F13" t="s">
         <v>850</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -4942,8 +5022,11 @@
       <c r="F14" t="s">
         <v>855</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -4962,8 +5045,11 @@
       <c r="F15" t="s">
         <v>860</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>80</v>
       </c>
@@ -4982,8 +5068,11 @@
       <c r="F16" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -5002,8 +5091,11 @@
       <c r="F17" t="s">
         <v>868</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -5022,8 +5114,11 @@
       <c r="F18" t="s">
         <v>873</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -5042,8 +5137,11 @@
       <c r="F19" t="s">
         <v>878</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -5062,8 +5160,11 @@
       <c r="F20" t="s">
         <v>883</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -5081,6 +5182,9 @@
       </c>
       <c r="F21" t="s">
         <v>888</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1102</v>
       </c>
     </row>
   </sheetData>
@@ -5094,7 +5198,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD6D6F06-13A7-4056-92CE-2FB1978C40F6}">
   <sheetPr codeName="Sheet14"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -5105,27 +5209,30 @@
     <col min="6" max="6" width="35.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B1" t="s">
         <v>1088</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1089</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1090</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1091</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1092</v>
       </c>
-      <c r="F1" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -5144,8 +5251,11 @@
       <c r="F2" t="s">
         <v>892</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -5164,8 +5274,11 @@
       <c r="F3" t="s">
         <v>897</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -5184,8 +5297,11 @@
       <c r="F4" t="s">
         <v>902</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5204,8 +5320,11 @@
       <c r="F5" t="s">
         <v>907</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -5224,8 +5343,11 @@
       <c r="F6" t="s">
         <v>912</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -5244,8 +5366,11 @@
       <c r="F7" t="s">
         <v>917</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -5264,8 +5389,11 @@
       <c r="F8" t="s">
         <v>922</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -5284,8 +5412,11 @@
       <c r="F9" t="s">
         <v>927</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -5304,8 +5435,11 @@
       <c r="F10" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -5324,8 +5458,11 @@
       <c r="F11" t="s">
         <v>937</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -5344,8 +5481,11 @@
       <c r="F12" t="s">
         <v>942</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -5364,8 +5504,11 @@
       <c r="F13" t="s">
         <v>947</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -5384,8 +5527,11 @@
       <c r="F14" t="s">
         <v>952</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -5404,8 +5550,11 @@
       <c r="F15" t="s">
         <v>957</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>80</v>
       </c>
@@ -5424,8 +5573,11 @@
       <c r="F16" t="s">
         <v>961</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="F17" t="s">
         <v>966</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -5464,8 +5619,11 @@
       <c r="F18" t="s">
         <v>971</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -5484,8 +5642,11 @@
       <c r="F19" t="s">
         <v>976</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -5504,8 +5665,11 @@
       <c r="F20" t="s">
         <v>981</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -5523,6 +5687,9 @@
       </c>
       <c r="F21" t="s">
         <v>986</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1102</v>
       </c>
     </row>
   </sheetData>
@@ -5536,7 +5703,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{123B9F92-F78B-4E5D-97CE-455155579D5F}">
   <sheetPr codeName="Sheet13"/>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -5545,53 +5712,33 @@
     <col min="4" max="4" width="35.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="36.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="59.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="81.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B1" t="s">
         <v>1088</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1089</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1090</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1091</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1092</v>
       </c>
-      <c r="F1" t="s">
-        <v>1093</v>
-      </c>
       <c r="G1" t="s">
-        <v>1102</v>
-      </c>
-      <c r="H1" t="s">
-        <v>1103</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1104</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1105</v>
-      </c>
-      <c r="K1" t="s">
-        <v>1106</v>
-      </c>
-      <c r="L1" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -5610,8 +5757,11 @@
       <c r="F2" t="s">
         <v>991</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -5630,8 +5780,11 @@
       <c r="F3" t="s">
         <v>996</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -5650,8 +5803,11 @@
       <c r="F4" t="s">
         <v>1001</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -5671,322 +5827,375 @@
         <v>1006</v>
       </c>
       <c r="G5" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
         <v>1007</v>
       </c>
-      <c r="H5" t="s">
+      <c r="C6" t="s">
         <v>1008</v>
       </c>
-      <c r="I5" t="s">
+      <c r="D6" t="s">
         <v>1009</v>
       </c>
-      <c r="J5" t="s">
+      <c r="E6" t="s">
         <v>1010</v>
       </c>
-      <c r="K5" t="s">
+      <c r="F6" t="s">
         <v>1011</v>
       </c>
-      <c r="L5" t="s">
+      <c r="G6" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
         <v>1012</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C7" t="s">
         <v>1013</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D7" t="s">
         <v>1014</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E7" t="s">
         <v>1015</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F7" t="s">
         <v>1016</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G7" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
         <v>1017</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C8" t="s">
         <v>1018</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D8" t="s">
         <v>1019</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E8" t="s">
         <v>1020</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F8" t="s">
         <v>1021</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G8" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s">
         <v>1022</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C9" t="s">
         <v>1023</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D9" t="s">
         <v>1024</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E9" t="s">
         <v>1025</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F9" t="s">
         <v>1026</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G9" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
         <v>1027</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C10" t="s">
         <v>1028</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D10" t="s">
         <v>1029</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E10" t="s">
         <v>1030</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F10" t="s">
         <v>1031</v>
       </c>
-      <c r="F9" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
       <c r="B11" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C11" t="s">
         <v>1033</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>1034</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>1035</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>1036</v>
       </c>
-      <c r="F11" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
       <c r="B12" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C12" t="s">
         <v>1038</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>1039</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>1040</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>1041</v>
       </c>
-      <c r="F12" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>62</v>
       </c>
       <c r="B13" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C13" t="s">
         <v>1043</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>1044</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>1045</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>1046</v>
       </c>
-      <c r="F13" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
       <c r="B14" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C14" t="s">
         <v>1048</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>1049</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>1050</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>1051</v>
       </c>
-      <c r="F14" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
       <c r="B15" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C15" t="s">
         <v>1053</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>1054</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>1055</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>1056</v>
       </c>
-      <c r="F15" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>80</v>
       </c>
       <c r="B16" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C16" t="s">
         <v>1058</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>1059</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>1060</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>1061</v>
       </c>
-      <c r="F16" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>86</v>
       </c>
       <c r="B17" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C17" t="s">
         <v>1063</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>1064</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>1065</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>1066</v>
       </c>
-      <c r="F17" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>92</v>
       </c>
       <c r="B18" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C18" t="s">
         <v>1068</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>1069</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>1070</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>1071</v>
       </c>
-      <c r="F18" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>98</v>
       </c>
       <c r="B19" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C19" t="s">
         <v>1073</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>1074</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>1075</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>1076</v>
       </c>
-      <c r="F19" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>103</v>
       </c>
       <c r="B20" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C20" t="s">
         <v>1078</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>1079</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>1080</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>1081</v>
       </c>
-      <c r="F20" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>108</v>
       </c>
       <c r="B21" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C21" t="s">
         <v>1083</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>1084</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>1085</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>1086</v>
       </c>
-      <c r="F21" t="s">
-        <v>1087</v>
+      <c r="G21" t="s">
+        <v>1102</v>
       </c>
     </row>
   </sheetData>
@@ -6000,7 +6209,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA6A2F45-2893-47C4-999E-DCF33FEA724D}">
   <sheetPr codeName="Sheet23"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6011,27 +6220,30 @@
     <col min="6" max="6" width="47.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B1" t="s">
         <v>1088</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1089</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1090</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1091</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1092</v>
       </c>
-      <c r="F1" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6050,8 +6262,11 @@
       <c r="F2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6070,8 +6285,11 @@
       <c r="F3" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -6090,8 +6308,11 @@
       <c r="F4" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6110,8 +6331,11 @@
       <c r="F5" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -6130,8 +6354,11 @@
       <c r="F6" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -6150,8 +6377,11 @@
       <c r="F7" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -6170,8 +6400,11 @@
       <c r="F8" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -6190,8 +6423,11 @@
       <c r="F9" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -6210,8 +6446,11 @@
       <c r="F10" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -6230,8 +6469,11 @@
       <c r="F11" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -6250,8 +6492,11 @@
       <c r="F12" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -6270,8 +6515,11 @@
       <c r="F13" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -6290,8 +6538,11 @@
       <c r="F14" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -6310,8 +6561,11 @@
       <c r="F15" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>80</v>
       </c>
@@ -6330,8 +6584,11 @@
       <c r="F16" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -6350,8 +6607,11 @@
       <c r="F17" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -6370,8 +6630,11 @@
       <c r="F18" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -6390,8 +6653,11 @@
       <c r="F19" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -6410,8 +6676,11 @@
       <c r="F20" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -6429,6 +6698,9 @@
       </c>
       <c r="F21" t="s">
         <v>213</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1102</v>
       </c>
     </row>
   </sheetData>
@@ -6442,7 +6714,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDBFA58F-C678-4973-A3B6-A35965566905}">
   <sheetPr codeName="Sheet22"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6453,27 +6725,30 @@
     <col min="6" max="6" width="42.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B1" t="s">
         <v>1088</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1089</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1090</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1091</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1092</v>
       </c>
-      <c r="F1" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6492,8 +6767,11 @@
       <c r="F2" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6512,8 +6790,11 @@
       <c r="F3" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -6532,8 +6813,11 @@
       <c r="F4" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6552,8 +6836,11 @@
       <c r="F5" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -6572,8 +6859,11 @@
       <c r="F6" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -6592,8 +6882,11 @@
       <c r="F7" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -6612,8 +6905,11 @@
       <c r="F8" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -6632,8 +6928,11 @@
       <c r="F9" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -6652,8 +6951,11 @@
       <c r="F10" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -6672,8 +6974,11 @@
       <c r="F11" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -6692,8 +6997,11 @@
       <c r="F12" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -6712,8 +7020,11 @@
       <c r="F13" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -6732,8 +7043,11 @@
       <c r="F14" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -6752,8 +7066,11 @@
       <c r="F15" t="s">
         <v>282</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>80</v>
       </c>
@@ -6772,8 +7089,11 @@
       <c r="F16" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -6792,8 +7112,11 @@
       <c r="F17" t="s">
         <v>292</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -6812,8 +7135,11 @@
       <c r="F18" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -6832,8 +7158,11 @@
       <c r="F19" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -6852,8 +7181,11 @@
       <c r="F20" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -6871,6 +7203,9 @@
       </c>
       <c r="F21" t="s">
         <v>312</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1102</v>
       </c>
     </row>
   </sheetData>
@@ -6884,7 +7219,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{019571A1-B9B9-41B0-845A-A79694C1B2C6}">
   <sheetPr codeName="Sheet21"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -6895,27 +7230,30 @@
     <col min="6" max="6" width="34.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B1" t="s">
         <v>1088</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1089</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1090</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1091</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1092</v>
       </c>
-      <c r="F1" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -6934,8 +7272,11 @@
       <c r="F2" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -6954,8 +7295,11 @@
       <c r="F3" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -6974,8 +7318,11 @@
       <c r="F4" t="s">
         <v>327</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6994,8 +7341,11 @@
       <c r="F5" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -7014,8 +7364,11 @@
       <c r="F6" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -7034,8 +7387,11 @@
       <c r="F7" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -7054,8 +7410,11 @@
       <c r="F8" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -7074,8 +7433,11 @@
       <c r="F9" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -7094,8 +7456,11 @@
       <c r="F10" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -7114,8 +7479,11 @@
       <c r="F11" t="s">
         <v>361</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -7134,8 +7502,11 @@
       <c r="F12" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -7154,8 +7525,11 @@
       <c r="F13" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -7174,8 +7548,11 @@
       <c r="F14" t="s">
         <v>376</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -7194,8 +7571,11 @@
       <c r="F15" t="s">
         <v>381</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>80</v>
       </c>
@@ -7214,8 +7594,11 @@
       <c r="F16" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -7234,8 +7617,11 @@
       <c r="F17" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -7254,8 +7640,11 @@
       <c r="F18" t="s">
         <v>395</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -7274,8 +7663,11 @@
       <c r="F19" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -7294,8 +7686,11 @@
       <c r="F20" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -7313,6 +7708,9 @@
       </c>
       <c r="F21" t="s">
         <v>409</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1102</v>
       </c>
     </row>
   </sheetData>
@@ -7326,7 +7724,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C32374E-C17B-4366-967D-3A3B02517E25}">
   <sheetPr codeName="Sheet20"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -7337,27 +7735,30 @@
     <col min="6" max="6" width="38.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B1" t="s">
         <v>1088</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1089</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1090</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1091</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1092</v>
       </c>
-      <c r="F1" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>410</v>
       </c>
@@ -7373,8 +7774,11 @@
       <c r="F2" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -7393,8 +7797,11 @@
       <c r="F3" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -7413,8 +7820,11 @@
       <c r="F4" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7433,8 +7843,11 @@
       <c r="F5" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -7453,8 +7866,11 @@
       <c r="F6" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -7473,8 +7889,11 @@
       <c r="F7" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -7493,8 +7912,11 @@
       <c r="F8" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -7513,8 +7935,11 @@
       <c r="F9" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -7533,8 +7958,11 @@
       <c r="F10" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -7553,8 +7981,11 @@
       <c r="F11" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -7573,8 +8004,11 @@
       <c r="F12" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -7593,8 +8027,11 @@
       <c r="F13" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -7613,8 +8050,11 @@
       <c r="F14" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -7633,8 +8073,11 @@
       <c r="F15" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>80</v>
       </c>
@@ -7653,8 +8096,11 @@
       <c r="F16" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -7673,8 +8119,11 @@
       <c r="F17" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -7693,8 +8142,11 @@
       <c r="F18" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -7713,8 +8165,11 @@
       <c r="F19" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -7733,8 +8188,11 @@
       <c r="F20" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -7752,6 +8210,9 @@
       </c>
       <c r="F21" t="s">
         <v>509</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1102</v>
       </c>
     </row>
   </sheetData>
@@ -7765,7 +8226,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F07545BB-7A46-4402-AD33-8DC03D2671CC}">
   <sheetPr codeName="Sheet19"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -7776,27 +8237,30 @@
     <col min="6" max="6" width="38.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B1" t="s">
         <v>1088</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1089</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1090</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1091</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1092</v>
       </c>
-      <c r="F1" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>410</v>
       </c>
@@ -7812,8 +8276,11 @@
       <c r="F2" t="s">
         <v>414</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -7832,8 +8299,11 @@
       <c r="F3" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -7852,8 +8322,11 @@
       <c r="F4" t="s">
         <v>424</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -7872,8 +8345,11 @@
       <c r="F5" t="s">
         <v>429</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -7892,8 +8368,11 @@
       <c r="F6" t="s">
         <v>434</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -7912,8 +8391,11 @@
       <c r="F7" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -7932,8 +8414,11 @@
       <c r="F8" t="s">
         <v>444</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -7952,8 +8437,11 @@
       <c r="F9" t="s">
         <v>449</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -7972,8 +8460,11 @@
       <c r="F10" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -7992,8 +8483,11 @@
       <c r="F11" t="s">
         <v>459</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -8012,8 +8506,11 @@
       <c r="F12" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -8032,8 +8529,11 @@
       <c r="F13" t="s">
         <v>469</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -8052,8 +8552,11 @@
       <c r="F14" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -8072,8 +8575,11 @@
       <c r="F15" t="s">
         <v>479</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>80</v>
       </c>
@@ -8092,8 +8598,11 @@
       <c r="F16" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -8112,8 +8621,11 @@
       <c r="F17" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -8132,8 +8644,11 @@
       <c r="F18" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -8152,8 +8667,11 @@
       <c r="F19" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -8172,8 +8690,11 @@
       <c r="F20" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -8191,6 +8712,9 @@
       </c>
       <c r="F21" t="s">
         <v>509</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1102</v>
       </c>
     </row>
   </sheetData>
@@ -8204,7 +8728,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E00B24CA-4E31-4FCD-BA17-923523AA0ABB}">
   <sheetPr codeName="Sheet18"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -8215,27 +8739,30 @@
     <col min="6" max="6" width="48.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B1" t="s">
         <v>1088</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1089</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1090</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1091</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1092</v>
       </c>
-      <c r="F1" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -8254,8 +8781,11 @@
       <c r="F2" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -8274,8 +8804,11 @@
       <c r="F3" t="s">
         <v>522</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -8294,8 +8827,11 @@
       <c r="F4" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -8314,8 +8850,11 @@
       <c r="F5" t="s">
         <v>532</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -8334,8 +8873,11 @@
       <c r="F6" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -8354,8 +8896,11 @@
       <c r="F7" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -8374,8 +8919,11 @@
       <c r="F8" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -8394,8 +8942,11 @@
       <c r="F9" t="s">
         <v>552</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -8414,8 +8965,11 @@
       <c r="F10" t="s">
         <v>557</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -8434,8 +8988,11 @@
       <c r="F11" t="s">
         <v>562</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -8454,8 +9011,11 @@
       <c r="F12" t="s">
         <v>567</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -8474,8 +9034,11 @@
       <c r="F13" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -8494,8 +9057,11 @@
       <c r="F14" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -8514,8 +9080,11 @@
       <c r="F15" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>80</v>
       </c>
@@ -8534,8 +9103,11 @@
       <c r="F16" t="s">
         <v>586</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -8554,8 +9126,11 @@
       <c r="F17" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -8574,8 +9149,11 @@
       <c r="F18" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -8594,8 +9172,11 @@
       <c r="F19" t="s">
         <v>601</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -8614,8 +9195,11 @@
       <c r="F20" t="s">
         <v>606</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -8633,6 +9217,9 @@
       </c>
       <c r="F21" t="s">
         <v>610</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1102</v>
       </c>
     </row>
   </sheetData>
@@ -8646,7 +9233,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F62751-BBFA-46A4-B72A-85224D3D5060}">
   <sheetPr codeName="Sheet17"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -8657,27 +9244,30 @@
     <col min="6" max="6" width="41.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B1" t="s">
         <v>1088</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1089</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1090</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1091</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1092</v>
       </c>
-      <c r="F1" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -8696,8 +9286,11 @@
       <c r="F2" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -8716,8 +9309,11 @@
       <c r="F3" t="s">
         <v>619</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -8736,8 +9332,11 @@
       <c r="F4" t="s">
         <v>624</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -8756,8 +9355,11 @@
       <c r="F5" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -8776,8 +9378,11 @@
       <c r="F6" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -8796,8 +9401,11 @@
       <c r="F7" t="s">
         <v>639</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -8816,8 +9424,11 @@
       <c r="F8" t="s">
         <v>644</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -8836,8 +9447,11 @@
       <c r="F9" t="s">
         <v>648</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -8856,8 +9470,11 @@
       <c r="F10" t="s">
         <v>653</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -8876,8 +9493,11 @@
       <c r="F11" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -8896,8 +9516,11 @@
       <c r="F12" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -8916,8 +9539,11 @@
       <c r="F13" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -8936,8 +9562,11 @@
       <c r="F14" t="s">
         <v>512</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -8956,8 +9585,11 @@
       <c r="F15" t="s">
         <v>676</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>80</v>
       </c>
@@ -8976,8 +9608,11 @@
       <c r="F16" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -8996,8 +9631,11 @@
       <c r="F17" t="s">
         <v>686</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -9016,8 +9654,11 @@
       <c r="F18" t="s">
         <v>691</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -9036,8 +9677,11 @@
       <c r="F19" t="s">
         <v>696</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -9056,8 +9700,11 @@
       <c r="F20" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -9075,6 +9722,9 @@
       </c>
       <c r="F21" t="s">
         <v>706</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1102</v>
       </c>
     </row>
   </sheetData>
@@ -9088,7 +9738,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C310508A-33EA-48E9-BF01-1851C8B77836}">
   <sheetPr codeName="Sheet16"/>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -9099,27 +9749,30 @@
     <col min="6" max="6" width="28.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B1" t="s">
         <v>1088</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1089</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1090</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1091</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1092</v>
       </c>
-      <c r="F1" t="s">
-        <v>1093</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -9138,8 +9791,11 @@
       <c r="F2" t="s">
         <v>711</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -9147,19 +9803,22 @@
         <v>712</v>
       </c>
       <c r="C3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="D3" t="s">
         <v>1094</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>1095</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>1096</v>
       </c>
-      <c r="F3" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -9178,8 +9837,11 @@
       <c r="F4" t="s">
         <v>717</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -9198,8 +9860,11 @@
       <c r="F5" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -9218,8 +9883,11 @@
       <c r="F6" t="s">
         <v>725</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -9238,8 +9906,11 @@
       <c r="F7" t="s">
         <v>730</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -9247,19 +9918,22 @@
         <v>731</v>
       </c>
       <c r="C8" t="s">
+        <v>1096</v>
+      </c>
+      <c r="D8" t="s">
         <v>1097</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>1098</v>
       </c>
-      <c r="E8" t="s">
-        <v>1099</v>
-      </c>
       <c r="F8" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1095</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -9267,19 +9941,22 @@
         <v>732</v>
       </c>
       <c r="C9" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E9" t="s">
         <v>1100</v>
       </c>
-      <c r="D9" t="s">
-        <v>1094</v>
-      </c>
-      <c r="E9" t="s">
-        <v>1101</v>
-      </c>
       <c r="F9" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1097</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -9298,8 +9975,11 @@
       <c r="F10" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -9318,8 +9998,11 @@
       <c r="F11" t="s">
         <v>742</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -9338,8 +10021,11 @@
       <c r="F12" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>62</v>
       </c>
@@ -9358,8 +10044,11 @@
       <c r="F13" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -9378,8 +10067,11 @@
       <c r="F14" t="s">
         <v>756</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
@@ -9398,8 +10090,11 @@
       <c r="F15" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>80</v>
       </c>
@@ -9418,8 +10113,11 @@
       <c r="F16" t="s">
         <v>766</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>86</v>
       </c>
@@ -9438,8 +10136,11 @@
       <c r="F17" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>92</v>
       </c>
@@ -9458,8 +10159,11 @@
       <c r="F18" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -9478,8 +10182,11 @@
       <c r="F19" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>103</v>
       </c>
@@ -9498,8 +10205,11 @@
       <c r="F20" t="s">
         <v>786</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>108</v>
       </c>
@@ -9517,6 +10227,9 @@
       </c>
       <c r="F21" t="s">
         <v>791</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1102</v>
       </c>
     </row>
   </sheetData>

--- a/Data/HRM/HRM_Quizzes.xlsx
+++ b/Data/HRM/HRM_Quizzes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PyCode\mba_quiz\Data\HRM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EF12E8-1A21-410D-B081-2978C2E5F55A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1587333B-0C99-45BC-BDFA-11BE52ACD746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="11" xr2:uid="{850D3C83-EED4-4016-BDB5-EF8EECDCB418}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="13" r:id="rId1"/>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="1103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="1107">
   <si>
     <t xml:space="preserve">Question 1 </t>
   </si>
@@ -3414,6 +3414,18 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Question 1</t>
   </si>
 </sst>
 </file>
@@ -3682,7 +3694,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{538EEDBA-9B73-431E-87C2-EC7AB5CB1DE7}" name="Invoked_Function" displayName="Invoked_Function" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{538EEDBA-9B73-431E-87C2-EC7AB5CB1DE7}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{F599255B-77EF-421C-BC43-F575F0D2D389}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{F599255B-77EF-421C-BC43-F575F0D2D389}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
     <tableColumn id="2" xr3:uid="{F9037DE6-3F6F-4929-8D3D-6CC3BA23249E}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{CC2ED0DA-041A-4783-90CB-838D55ADB421}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{CE685B90-37D4-407A-9793-AEBBE45D2408}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3698,7 +3710,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{A458C2F0-5314-46D4-86CC-16A0BB56D714}" name="Invoked_Function__10" displayName="Invoked_Function__10" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{A458C2F0-5314-46D4-86CC-16A0BB56D714}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A3B2750A-27F3-4A7E-BEB8-FDAC5FD687EF}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{A3B2750A-27F3-4A7E-BEB8-FDAC5FD687EF}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{3E1DAE0D-A68A-4B90-8C95-493D26B5F28C}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{A8A1A4F9-D04D-44D8-9948-311EE9B9CA0F}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{7C39C9C2-AD88-444F-927B-6D9263104D72}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3746,7 +3758,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{D476988A-A03F-43E3-953D-057325572397}" name="Invoked_Function__2" displayName="Invoked_Function__2" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{D476988A-A03F-43E3-953D-057325572397}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{605EF333-5722-493C-82E0-12B760CE7067}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{605EF333-5722-493C-82E0-12B760CE7067}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{042D1B72-808B-4960-85C5-536138CEE3DE}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{5D059C41-8EED-4120-B4F8-67E6CEC2B24C}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{20CE8CD6-7C5E-4EA2-A135-BAA225C79362}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3762,7 +3774,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="21" xr:uid="{2493896C-A371-4C58-AE23-34F325B82283}" name="Invoked_Function__3" displayName="Invoked_Function__3" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{2493896C-A371-4C58-AE23-34F325B82283}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{C621114B-B9CA-462D-BFAF-247A7FD9C7E6}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{C621114B-B9CA-462D-BFAF-247A7FD9C7E6}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{5B729A9B-6D93-48C6-A805-530D7AFB6651}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{1AABFCC3-CDF8-4CCE-88C8-5EE20FBBE7D8}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{86BE7E48-3954-4F04-852D-6AD757F15566}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3778,7 +3790,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="22" xr:uid="{8CF9526B-0C69-43D2-8248-B78E06868964}" name="Invoked_Function__4" displayName="Invoked_Function__4" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{8CF9526B-0C69-43D2-8248-B78E06868964}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{8E99948E-F064-4567-A246-73D9CA11E083}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{8E99948E-F064-4567-A246-73D9CA11E083}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{9B57E41B-6B27-4270-AF9D-6800752C267E}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{F6FCAF3B-8841-4362-AB13-A1B34B118553}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{F401941F-B30C-47C9-A80E-8A412A8BD088}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3794,7 +3806,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{630DF0C7-A642-464E-B088-DD948311C487}" name="Invoked_Function__5" displayName="Invoked_Function__5" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{630DF0C7-A642-464E-B088-DD948311C487}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{49F8398D-86A9-4EAE-8952-759BCE4D98AF}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{49F8398D-86A9-4EAE-8952-759BCE4D98AF}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{B31E6E79-19D8-41A9-B943-CCDC9E1047EA}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{5046AFE6-EDFF-4D24-9AB4-8C345BADEC3D}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{82A3762B-C370-412F-9FA6-86FFBC9DD42D}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3810,7 +3822,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="24" xr:uid="{F878B18C-1BF7-4F22-B23B-22B0371F00E7}" name="Invoked_Function__6" displayName="Invoked_Function__6" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{F878B18C-1BF7-4F22-B23B-22B0371F00E7}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{C25841B3-DDDF-42A6-BBEE-14A7961B8950}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{C25841B3-DDDF-42A6-BBEE-14A7961B8950}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{BA4C1515-CA9D-4DFF-B08D-714CA9B378AA}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{AEE8A806-C2B4-4001-AFD8-5ACC84846AA0}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{8BC6E0BA-5FF4-460B-B699-EEC07FEEE59A}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3826,7 +3838,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{8C2F89B4-E03C-442F-B7E8-6AA63C7285D9}" name="Invoked_Function__7" displayName="Invoked_Function__7" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{8C2F89B4-E03C-442F-B7E8-6AA63C7285D9}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{2D8418AB-FCD1-4B6F-AF10-F9094E63B6DA}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{2D8418AB-FCD1-4B6F-AF10-F9094E63B6DA}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{5FE58BE0-7E4D-461A-A1C1-AE690F3724ED}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{30DD1391-CD8B-4CDF-8501-69325B214960}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{0182432B-D43D-45E0-B683-16CEF8E9E6DC}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3842,7 +3854,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{486C2A8A-BAC1-4CF8-9F56-547EAA3A4E83}" name="Invoked_Function__8" displayName="Invoked_Function__8" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{486C2A8A-BAC1-4CF8-9F56-547EAA3A4E83}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{64A53E32-7AA1-4F11-BD01-CDA508EFC0CA}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{64A53E32-7AA1-4F11-BD01-CDA508EFC0CA}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{3DBC2F52-F019-457B-93B7-EAF3F474C325}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{127D2DFA-24B3-4067-B62F-339E00C85C62}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{A77ED5BD-F15F-4558-AF9C-BF5BABB0266B}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -3858,7 +3870,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{3ED021C4-F6DF-4C65-96B4-CA439D902DAF}" name="Invoked_Function__9" displayName="Invoked_Function__9" ref="A1:G21" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:G21" xr:uid="{3ED021C4-F6DF-4C65-96B4-CA439D902DAF}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{451FD237-E5B3-4EF2-BC40-19A77FC26C18}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{451FD237-E5B3-4EF2-BC40-19A77FC26C18}" uniqueName="1" name="QuestionID" queryTableFieldId="1" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{248CB54E-57CF-448A-9A91-AC65DB84B0E7}" uniqueName="2" name="Question" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{EE822D66-B546-4BB8-981B-E65761A57BD4}" uniqueName="3" name="Option_A" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{76E01E24-686A-47BC-94FC-F85B09563D65}" uniqueName="4" name="Option_B" queryTableFieldId="4"/>
@@ -4242,7 +4254,7 @@
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4265,7 +4277,7 @@
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -4311,7 +4323,7 @@
         <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4334,7 +4346,7 @@
         <v>29</v>
       </c>
       <c r="G6" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4357,7 +4369,7 @@
         <v>35</v>
       </c>
       <c r="G7" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4380,7 +4392,7 @@
         <v>41</v>
       </c>
       <c r="G8" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -4403,7 +4415,7 @@
         <v>47</v>
       </c>
       <c r="G9" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -4426,7 +4438,7 @@
         <v>16</v>
       </c>
       <c r="G10" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -4449,7 +4461,7 @@
         <v>56</v>
       </c>
       <c r="G11" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4472,7 +4484,7 @@
         <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -4495,7 +4507,7 @@
         <v>67</v>
       </c>
       <c r="G13" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -4518,7 +4530,7 @@
         <v>73</v>
       </c>
       <c r="G14" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -4541,7 +4553,7 @@
         <v>79</v>
       </c>
       <c r="G15" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -4564,7 +4576,7 @@
         <v>85</v>
       </c>
       <c r="G16" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -4587,7 +4599,7 @@
         <v>91</v>
       </c>
       <c r="G17" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -4633,7 +4645,7 @@
         <v>102</v>
       </c>
       <c r="G19" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -4656,7 +4668,7 @@
         <v>107</v>
       </c>
       <c r="G20" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -4679,7 +4691,7 @@
         <v>113</v>
       </c>
       <c r="G21" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
   </sheetData>
@@ -4747,7 +4759,7 @@
         <v>796</v>
       </c>
       <c r="G2" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4770,7 +4782,7 @@
         <v>801</v>
       </c>
       <c r="G3" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -4793,7 +4805,7 @@
         <v>806</v>
       </c>
       <c r="G4" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4816,7 +4828,7 @@
         <v>811</v>
       </c>
       <c r="G5" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4839,7 +4851,7 @@
         <v>816</v>
       </c>
       <c r="G6" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4862,7 +4874,7 @@
         <v>821</v>
       </c>
       <c r="G7" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -4885,7 +4897,7 @@
         <v>826</v>
       </c>
       <c r="G8" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -4931,7 +4943,7 @@
         <v>835</v>
       </c>
       <c r="G10" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -4954,7 +4966,7 @@
         <v>840</v>
       </c>
       <c r="G11" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -4977,7 +4989,7 @@
         <v>845</v>
       </c>
       <c r="G12" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -5023,7 +5035,7 @@
         <v>855</v>
       </c>
       <c r="G14" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -5046,7 +5058,7 @@
         <v>860</v>
       </c>
       <c r="G15" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -5092,7 +5104,7 @@
         <v>868</v>
       </c>
       <c r="G17" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -5115,7 +5127,7 @@
         <v>873</v>
       </c>
       <c r="G18" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -5138,7 +5150,7 @@
         <v>878</v>
       </c>
       <c r="G19" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5161,7 +5173,7 @@
         <v>883</v>
       </c>
       <c r="G20" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5252,7 +5264,7 @@
         <v>892</v>
       </c>
       <c r="G2" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -5275,7 +5287,7 @@
         <v>897</v>
       </c>
       <c r="G3" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -5321,7 +5333,7 @@
         <v>907</v>
       </c>
       <c r="G5" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -5344,7 +5356,7 @@
         <v>912</v>
       </c>
       <c r="G6" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -5413,7 +5425,7 @@
         <v>927</v>
       </c>
       <c r="G9" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -5436,7 +5448,7 @@
         <v>932</v>
       </c>
       <c r="G10" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -5482,7 +5494,7 @@
         <v>942</v>
       </c>
       <c r="G12" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -5505,7 +5517,7 @@
         <v>947</v>
       </c>
       <c r="G13" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -5528,7 +5540,7 @@
         <v>952</v>
       </c>
       <c r="G14" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -5620,7 +5632,7 @@
         <v>971</v>
       </c>
       <c r="G18" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -5643,7 +5655,7 @@
         <v>976</v>
       </c>
       <c r="G19" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5666,7 +5678,7 @@
         <v>981</v>
       </c>
       <c r="G20" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5689,7 +5701,7 @@
         <v>986</v>
       </c>
       <c r="G21" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
   </sheetData>
@@ -5758,7 +5770,7 @@
         <v>991</v>
       </c>
       <c r="G2" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -5781,7 +5793,7 @@
         <v>996</v>
       </c>
       <c r="G3" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -5804,7 +5816,7 @@
         <v>1001</v>
       </c>
       <c r="G4" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -5850,7 +5862,7 @@
         <v>1011</v>
       </c>
       <c r="G6" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -5919,7 +5931,7 @@
         <v>1026</v>
       </c>
       <c r="G9" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -5942,7 +5954,7 @@
         <v>1031</v>
       </c>
       <c r="G10" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -5965,7 +5977,7 @@
         <v>1036</v>
       </c>
       <c r="G11" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -5988,7 +6000,7 @@
         <v>1041</v>
       </c>
       <c r="G12" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -6034,7 +6046,7 @@
         <v>1051</v>
       </c>
       <c r="G14" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6057,7 +6069,7 @@
         <v>1056</v>
       </c>
       <c r="G15" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -6080,7 +6092,7 @@
         <v>1061</v>
       </c>
       <c r="G16" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -6126,7 +6138,7 @@
         <v>1071</v>
       </c>
       <c r="G18" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -6149,7 +6161,7 @@
         <v>1076</v>
       </c>
       <c r="G19" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -6172,7 +6184,7 @@
         <v>1081</v>
       </c>
       <c r="G20" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -6195,7 +6207,7 @@
         <v>1086</v>
       </c>
       <c r="G21" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
   </sheetData>
@@ -6332,7 +6344,7 @@
         <v>133</v>
       </c>
       <c r="G5" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -6355,7 +6367,7 @@
         <v>138</v>
       </c>
       <c r="G6" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6378,7 +6390,7 @@
         <v>143</v>
       </c>
       <c r="G7" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6401,7 +6413,7 @@
         <v>148</v>
       </c>
       <c r="G8" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -6424,7 +6436,7 @@
         <v>153</v>
       </c>
       <c r="G9" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6447,7 +6459,7 @@
         <v>158</v>
       </c>
       <c r="G10" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6470,7 +6482,7 @@
         <v>163</v>
       </c>
       <c r="G11" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6493,7 +6505,7 @@
         <v>168</v>
       </c>
       <c r="G12" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -6516,7 +6528,7 @@
         <v>173</v>
       </c>
       <c r="G13" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -6539,7 +6551,7 @@
         <v>178</v>
       </c>
       <c r="G14" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -6562,7 +6574,7 @@
         <v>183</v>
       </c>
       <c r="G15" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -6585,7 +6597,7 @@
         <v>188</v>
       </c>
       <c r="G16" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -6608,7 +6620,7 @@
         <v>193</v>
       </c>
       <c r="G17" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -6631,7 +6643,7 @@
         <v>198</v>
       </c>
       <c r="G18" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -6654,7 +6666,7 @@
         <v>203</v>
       </c>
       <c r="G19" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -6677,7 +6689,7 @@
         <v>208</v>
       </c>
       <c r="G20" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -6700,7 +6712,7 @@
         <v>213</v>
       </c>
       <c r="G21" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
   </sheetData>
@@ -6768,7 +6780,7 @@
         <v>218</v>
       </c>
       <c r="G2" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -6791,7 +6803,7 @@
         <v>223</v>
       </c>
       <c r="G3" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -6814,7 +6826,7 @@
         <v>228</v>
       </c>
       <c r="G4" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -6860,7 +6872,7 @@
         <v>238</v>
       </c>
       <c r="G6" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -6883,7 +6895,7 @@
         <v>243</v>
       </c>
       <c r="G7" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -6929,7 +6941,7 @@
         <v>252</v>
       </c>
       <c r="G9" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -6952,7 +6964,7 @@
         <v>257</v>
       </c>
       <c r="G10" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -6975,7 +6987,7 @@
         <v>262</v>
       </c>
       <c r="G11" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -6998,7 +7010,7 @@
         <v>267</v>
       </c>
       <c r="G12" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -7021,7 +7033,7 @@
         <v>272</v>
       </c>
       <c r="G13" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -7044,7 +7056,7 @@
         <v>277</v>
       </c>
       <c r="G14" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -7067,7 +7079,7 @@
         <v>282</v>
       </c>
       <c r="G15" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -7113,7 +7125,7 @@
         <v>292</v>
       </c>
       <c r="G17" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -7136,7 +7148,7 @@
         <v>297</v>
       </c>
       <c r="G18" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -7159,7 +7171,7 @@
         <v>302</v>
       </c>
       <c r="G19" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -7182,7 +7194,7 @@
         <v>307</v>
       </c>
       <c r="G20" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -7205,7 +7217,7 @@
         <v>312</v>
       </c>
       <c r="G21" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
   </sheetData>
@@ -7273,7 +7285,7 @@
         <v>317</v>
       </c>
       <c r="G2" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -7296,7 +7308,7 @@
         <v>322</v>
       </c>
       <c r="G3" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7319,7 +7331,7 @@
         <v>327</v>
       </c>
       <c r="G4" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -7365,7 +7377,7 @@
         <v>337</v>
       </c>
       <c r="G6" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7411,7 +7423,7 @@
         <v>346</v>
       </c>
       <c r="G8" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7434,7 +7446,7 @@
         <v>351</v>
       </c>
       <c r="G9" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -7457,7 +7469,7 @@
         <v>356</v>
       </c>
       <c r="G10" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -7480,7 +7492,7 @@
         <v>361</v>
       </c>
       <c r="G11" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -7526,7 +7538,7 @@
         <v>371</v>
       </c>
       <c r="G13" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -7595,7 +7607,7 @@
         <v>386</v>
       </c>
       <c r="G16" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -7618,7 +7630,7 @@
         <v>391</v>
       </c>
       <c r="G17" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -7664,7 +7676,7 @@
         <v>400</v>
       </c>
       <c r="G19" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -7687,7 +7699,7 @@
         <v>116</v>
       </c>
       <c r="G20" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -7710,7 +7722,7 @@
         <v>409</v>
       </c>
       <c r="G21" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
   </sheetData>
@@ -7759,6 +7771,9 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1106</v>
+      </c>
       <c r="B2" t="s">
         <v>410</v>
       </c>
@@ -7775,7 +7790,7 @@
         <v>414</v>
       </c>
       <c r="G2" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -7798,7 +7813,7 @@
         <v>419</v>
       </c>
       <c r="G3" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7821,7 +7836,7 @@
         <v>424</v>
       </c>
       <c r="G4" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -7844,7 +7859,7 @@
         <v>429</v>
       </c>
       <c r="G5" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -7867,7 +7882,7 @@
         <v>434</v>
       </c>
       <c r="G6" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -7890,7 +7905,7 @@
         <v>439</v>
       </c>
       <c r="G7" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -7913,7 +7928,7 @@
         <v>444</v>
       </c>
       <c r="G8" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -7936,7 +7951,7 @@
         <v>449</v>
       </c>
       <c r="G9" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -7982,7 +7997,7 @@
         <v>459</v>
       </c>
       <c r="G11" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -8005,7 +8020,7 @@
         <v>464</v>
       </c>
       <c r="G12" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -8051,7 +8066,7 @@
         <v>474</v>
       </c>
       <c r="G14" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8074,7 +8089,7 @@
         <v>479</v>
       </c>
       <c r="G15" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8143,7 +8158,7 @@
         <v>494</v>
       </c>
       <c r="G18" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -8166,7 +8181,7 @@
         <v>499</v>
       </c>
       <c r="G19" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -8189,7 +8204,7 @@
         <v>504</v>
       </c>
       <c r="G20" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -8212,7 +8227,7 @@
         <v>509</v>
       </c>
       <c r="G21" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
   </sheetData>
@@ -8261,6 +8276,9 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1106</v>
+      </c>
       <c r="B2" t="s">
         <v>410</v>
       </c>
@@ -8277,7 +8295,7 @@
         <v>414</v>
       </c>
       <c r="G2" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -8346,7 +8364,7 @@
         <v>429</v>
       </c>
       <c r="G5" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -8369,7 +8387,7 @@
         <v>434</v>
       </c>
       <c r="G6" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -8392,7 +8410,7 @@
         <v>439</v>
       </c>
       <c r="G7" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8438,7 +8456,7 @@
         <v>449</v>
       </c>
       <c r="G9" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -8461,7 +8479,7 @@
         <v>454</v>
       </c>
       <c r="G10" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -8484,7 +8502,7 @@
         <v>459</v>
       </c>
       <c r="G11" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -8530,7 +8548,7 @@
         <v>469</v>
       </c>
       <c r="G13" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -8553,7 +8571,7 @@
         <v>474</v>
       </c>
       <c r="G14" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -8576,7 +8594,7 @@
         <v>479</v>
       </c>
       <c r="G15" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -8599,7 +8617,7 @@
         <v>484</v>
       </c>
       <c r="G16" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -8622,7 +8640,7 @@
         <v>489</v>
       </c>
       <c r="G17" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -8714,7 +8732,7 @@
         <v>509</v>
       </c>
       <c r="G21" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
   </sheetData>
@@ -8782,7 +8800,7 @@
         <v>517</v>
       </c>
       <c r="G2" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -8851,7 +8869,7 @@
         <v>532</v>
       </c>
       <c r="G5" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -8874,7 +8892,7 @@
         <v>537</v>
       </c>
       <c r="G6" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -8897,7 +8915,7 @@
         <v>542</v>
       </c>
       <c r="G7" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -8920,7 +8938,7 @@
         <v>547</v>
       </c>
       <c r="G8" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -8966,7 +8984,7 @@
         <v>557</v>
       </c>
       <c r="G10" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -9012,7 +9030,7 @@
         <v>567</v>
       </c>
       <c r="G12" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -9035,7 +9053,7 @@
         <v>572</v>
       </c>
       <c r="G13" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -9058,7 +9076,7 @@
         <v>577</v>
       </c>
       <c r="G14" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -9081,7 +9099,7 @@
         <v>581</v>
       </c>
       <c r="G15" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -9104,7 +9122,7 @@
         <v>586</v>
       </c>
       <c r="G16" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -9150,7 +9168,7 @@
         <v>596</v>
       </c>
       <c r="G18" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -9196,7 +9214,7 @@
         <v>606</v>
       </c>
       <c r="G20" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -9219,7 +9237,7 @@
         <v>610</v>
       </c>
       <c r="G21" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
   </sheetData>
@@ -9287,7 +9305,7 @@
         <v>614</v>
       </c>
       <c r="G2" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -9310,7 +9328,7 @@
         <v>619</v>
       </c>
       <c r="G3" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -9356,7 +9374,7 @@
         <v>629</v>
       </c>
       <c r="G5" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -9379,7 +9397,7 @@
         <v>634</v>
       </c>
       <c r="G6" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -9425,7 +9443,7 @@
         <v>644</v>
       </c>
       <c r="G8" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -9471,7 +9489,7 @@
         <v>653</v>
       </c>
       <c r="G10" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -9494,7 +9512,7 @@
         <v>658</v>
       </c>
       <c r="G11" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -9517,7 +9535,7 @@
         <v>662</v>
       </c>
       <c r="G12" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -9540,7 +9558,7 @@
         <v>667</v>
       </c>
       <c r="G13" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -9563,7 +9581,7 @@
         <v>512</v>
       </c>
       <c r="G14" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -9609,7 +9627,7 @@
         <v>681</v>
       </c>
       <c r="G16" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -9632,7 +9650,7 @@
         <v>686</v>
       </c>
       <c r="G17" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -9655,7 +9673,7 @@
         <v>691</v>
       </c>
       <c r="G18" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -9678,7 +9696,7 @@
         <v>696</v>
       </c>
       <c r="G19" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -9701,7 +9719,7 @@
         <v>701</v>
       </c>
       <c r="G20" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -9724,7 +9742,7 @@
         <v>706</v>
       </c>
       <c r="G21" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
   </sheetData>
@@ -9792,7 +9810,7 @@
         <v>711</v>
       </c>
       <c r="G2" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -9815,7 +9833,7 @@
         <v>1096</v>
       </c>
       <c r="G3" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -9838,7 +9856,7 @@
         <v>717</v>
       </c>
       <c r="G4" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -9861,7 +9879,7 @@
         <v>720</v>
       </c>
       <c r="G5" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -9884,7 +9902,7 @@
         <v>725</v>
       </c>
       <c r="G6" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -9907,7 +9925,7 @@
         <v>730</v>
       </c>
       <c r="G7" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -9953,7 +9971,7 @@
         <v>1097</v>
       </c>
       <c r="G9" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -9999,7 +10017,7 @@
         <v>742</v>
       </c>
       <c r="G11" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -10091,7 +10109,7 @@
         <v>761</v>
       </c>
       <c r="G15" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -10114,7 +10132,7 @@
         <v>766</v>
       </c>
       <c r="G16" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -10137,7 +10155,7 @@
         <v>771</v>
       </c>
       <c r="G17" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -10160,7 +10178,7 @@
         <v>776</v>
       </c>
       <c r="G18" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -10183,7 +10201,7 @@
         <v>781</v>
       </c>
       <c r="G19" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -10206,7 +10224,7 @@
         <v>786</v>
       </c>
       <c r="G20" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
